--- a/database/datas-secondaire.xlsx
+++ b/database/datas-secondaire.xlsx
@@ -2,6 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
+  <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="Ngqs+Qw/HkdEVfGNxVe6llRh6nfFoUX/4I3eHgMLQLNN7ep81+xNT0ZOKnOPCBfmPIYdetAoBbbzc0Kyb+EtyA==" workbookSaltValue="OAiI32DplVK5S22sIcL8lA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
@@ -38313,13 +38314,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{1566B0B8-0501-4CCA-8A10-C799F43934CF}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{C2AB401A-2627-4389-AEE3-4A7E2F7D030F}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"1ère,2ème,3ème,4ème,5ème,6ème,7ème E.B,8ème E.B"</xm:f>
           </x14:formula1>
           <xm:sqref>N8:N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N35 N36 N37 N38 N39 N40 N41 N42 N43 N44 N45 N46 N47 N48 N49 N50 N51 N52 N53 N54 N55 N56 N57 N58 N59 N60 N61 N62 N63 N64 N65 N66 N67 N68 N69 N70 N71 N72 N73 N74 N75 N76 N77 N78 N79 N80 N81 N82 N83 N84 N85 N86 N87 N88 N89 N90 N91 N92 N93 N94 N95 N96 N97 N98 N99 N100 N101 N102 N103 N104 N105 N106 N107 N108 N109 N110 N111 N112 N113 N114 N115 N116 N117 N118 N119 N120 N121 N122 N123 N124 N125 N126 N127 N128 N129 N130 N131 N132 N133 N134 N135 N136 N137 N138 N139 N140 N141 N142 N143 N144 N145 N146 N147 N148 N149 N150 N151 N152 N153 N154 N155 N156 N157 N158 N159 N160 N161 N162 N163 N164 N165 N166 N167 N168 N169 N170 N171 N172 N173 N174 N175 N176 N177 N178 N179 N180 N181 N182 N183 N184 N185 N186 N187 N188 N189 N190 N191 N192 N193 N194 N195 N196 N197 N198 N199 N200 N201 N202 N203 N204 N205 N206 N207 N208 N209 N210 N211 N212 N213 N214 N215 N216 N217 N218 N219 N220 N221 N222 N223 N224 N225 N226 N227 N228 N229 N230 N231 N232 N233 N234 N235 N236 N237 N238 N239 N240 N241 N242 N243 N244 N245 N246 N247 N248 N249 N250 N251 N252 N253 N254 N255 N256 N257 N258 N259 N260 N261 N262 N263 N264 N265 N266 N267 N268 N269 N270 N271 N272 N273 N274 N275 N276 N277 N278 N279 N280 N281 N282 N283 N284 N285 N286 N287 N288 N289 N290 N291 N292 N293 N294 N295 N296 N297 N298 N299 N300 N301 N302 N303 N304 N305 N306 N307 N308 N309 N310 N311 N312 N313 N314 N315 N316 N317 N318 N319 N320 N321 N322 N323 N324 N325 N326 N327 N328 N329 N330 N331 N332 N333 N334 N335 N336 N337 N338 N339 N340 N341 N342 N343 N344 N345 N346 N347 N348 N349 N350 N351 N352 N353 N354 N355 N356 N357 N358 N359 N360 N361 N362 N363 N364 N365 N366 N367 N368 N369 N370 N371 N372 N373 N374 N375 N376 N377 N378 N379 N380 N381 N382 N383 N384 N385 N386 N387 N388 N389 N390 N391 N392 N393 N394 N395 N396 N397 N398 N399 N400 N401 N402 N403 N404 N405 N406 N407 N408 N409 N410 N411 N412 N413 N414 N415 N416 N417 N418 N419 N420 N421 N422 N423 N424 N425 N426 N427 N428 N429 N430 N431 N432 N433 N434 N435 N436 N437 N438 N439 N440 N441 N442 N443 N444 N445 N446 N447 N448 N449 N450 N451 N452 N453 N454 N455 N456 N457 N458 N459 N460 N461 N462 N463 N464 N465 N466 N467 N468 N469 N470 N471 N472 N473 N474 N475 N476 N477 N478 N479 N480 N481 N482 N483 N484 N485 N486 N487 N488 N489 N490 N491 N492 N493 N494 N495 N496 N497 N498 N499 N500 N501 N502 N503 N504 N505 N506 N507 N508 N509 N510 N511 N512 N513 N514 N515 N516 N517 N518 N519 N520 N521 N522 N523 N524 N525 N526 N527 N528 N529 N530 N531 N532 N533 N534 N535 N536 N537 N538 N539 N540 N541 N542 N543 N544 N545 N546 N547 N548 N549 N550 N551 N552 N553 N554 N555 N556 N557 N558 N559 N560 N561 N562 N563 N564 N565 N566 N567 N568 N569 N570 N571 N572 N573 N574 N575 N576 N577 N578 N579 N580 N581 N582 N583 N584 N585 N586 N587 N588 N589 N590 N591 N592 N593 N594 N595 N596 N597 N598 N599 N600 N601 N602 N603 N604 N605 N606 N607 N608 N609 N610 N611 N612 N613 N614 N615 N616 N617 N618 N619 N620 N621 N622 N623 N624 N625 N626 N627 N628 N629 N630 N631 N632 N633 N634 N635 N636 N637 N638 N639 N640 N641 N642 N643 N644 N645 N646 N647 N648 N649 N650 N651 N652 N653 N654 N655 N656 N657 N658 N659 N660 N661 N662 N663 N664 N665 N666 N667 N668 N669 N670 N671 N672 N673 N674 N675 N676 N677 N678 N679 N680 N681 N682 N683 N684 N685 N686 N687 N688 N689 N690 N691 N692 N693 N694 N695 N696 N697 N698 N699 N700 N701 N702 N703 N704 N705 N706 N707 N708 N709 N710 N711 N712 N713 N714 N715 N716 N717 N718 N719 N720 N721 N722 N723 N724 N725 N726 N727 N728 N729 N730 N731 N732 N733 N734 N735 N736 N737 N738 N739 N740 N741 N742 N743 N744 N745 N746 N747 N748 N749 N750 N751 N752 N753 N754 N755 N756 N757 N758 N759 N760 N761 N762 N763 N764 N765 N766 N767 N768 N769 N770 N771 N772 N773 N774 N775 N776 N777 N778 N779 N780 N781 N782 N783 N784 N785 N786 N787 N788 N789 N790 N791 N792 N793 N794 N795 N796 N797 N798 N799 N800 N801 N802 N803 N804 N805 N806 N807 N808 N809 N810 N811 N812 N813 N814 N815 N816 N817 N818 N819 N820 N821 N822 N823 N824 N825 N826 N827 N828 N829 N830 N831 N832 N833 N834 N835 N836 N837 N838 N839 N840 N841 N842 N843 N844 N845 N846 N847 N848 N849 N850 N851 N852 N853 N854 N855 N856 N857 N858 N859 N860 N861 N862 N863 N864 N865 N866 N867 N868 N869 N870 N871 N872 N873 N874 N875 N876 N877 N878 N879 N880 N881 N882 N883 N884 N885 N886 N887 N888 N889 N890 N891 N892 N893 N894 N895 N896 N897 N898 N899 N900 N901 N902 N903 N904 N905 N906 N907 N908 N909 N910 N911 N912 N913 N914 N915 N916 N917 N918 N919 N920 N921 N922 N923 N924 N925 N926 N927 N928 N929 N930 N931 N932 N933 N934 N935 N936 N937 N938 N939 N940 N941 N942 N943 N944 N945 N946 N947 N948 N949 N950 N951 N952 N953 N954 N955 N956 N957 N958 N959 N960 N961 N962 N963 N964 N965 N966 N967 N968 N969 N970 N971 N972 N973 N974 N975 N976 N977 N978 N979 N980 N981 N982 N983 N984 N985 N986 N987 N988 N989 N990 N991 N992 N993 N994 N995 N996 N997 N998 N999 N1000 N1001 N1002 N1003 N1004 N1005 N1006 N1007 N1008 N1009 N1010 N1011 N1012 N1013 N1014 N1015 N1016 N1017 N1018 N1019 N1020 N1021 N1022 N1023 N1024 N1025 N1026 N1027 N1028 N1029 N1030 N1031 N1032 N1033 N1034 N1035 N1036 N1037 N1038 N1039 N1040 N1041 N1042 N1043 N1044 N1045 N1046 N1047 N1048 N1049 N1050 N1051 N1052 N1053 N1054 N1055 N1056 N1057 N1058 N1059 N1060 N1061 N1062 N1063 N1064 N1065 N1066 N1067 N1068 N1069 N1070 N1071 N1072 N1073 N1074 N1075 N1076 N1077 N1078 N1079 N1080 N1081 N1082 N1083 N1084 N1085 N1086 N1087 N1088 N1089 N1090 N1091 N1092 N1093 N1094 N1095 N1096 N1097 N1098 N1099 N1100 N1101 N1102 N1103 N1104 N1105 N1106 N1107 N1108 N1109 N1110 N1111 N1112 N1113 N1114 N1115 N1116 N1117 N1118 N1119 N1120 N1121 N1122 N1123 N1124 N1125 N1126 N1127 N1128 N1129 N1130 N1131 N1132 N1133 N1134 N1135 N1136 N1137 N1138 N1139 N1140 N1141 N1142 N1143 N1144 N1145 N1146 N1147 N1148 N1149 N1150 N1151 N1152 N1153 N1154 N1155 N1156 N1157 N1158 N1159 N1160 N1161 N1162 N1163 N1164 N1165 N1166 N1167 N1168 N1169 N1170 N1171 N1172 N1173 N1174 N1175 N1176 N1177 N1178 N1179 N1180 N1181 N1182 N1183 N1184 N1185 N1186 N1187 N1188 N1189 N1190 N1191 N1192 N1193 N1194 N1195 N1196 N1197 N1198 N1199 N1200 N1201 N1202 N1203 N1204 N1205 N1206 N1207 N1208 N1209 N1210 N1211 N1212 N1213 N1214 N1215 N1216 N1217 N1218 N1219 N1220 N1221 N1222 N1223 N1224 N1225 N1226 N1227 N1228 N1229 N1230 N1231 N1232 N1233 N1234 N1235 N1236 N1237 N1238 N1239 N1240 N1241 N1242 N1243 N1244 N1245 N1246 N1247 N1248 N1249 N1250 N1251 N1252 N1253 N1254 N1255 N1256 N1257 N1258 N1259 N1260 N1261 N1262 N1263 N1264 N1265 N1266 N1267 N1268 N1269 N1270 N1271 N1272 N1273 N1274 N1275 N1276 N1277 N1278 N1279 N1280 N1281 N1282 N1283 N1284 N1285 N1286 N1287 N1288 N1289 N1290 N1291 N1292 N1293 N1294 N1295 N1296 N1297 N1298 N1299 N1300 N1301 N1302 N1303 N1304 N1305 N1306 N1307 N1308 N1309 N1310 N1311 N1312 N1313 N1314 N1315 N1316 N1317 N1318 N1319 N1320 N1321 N1322 N1323 N1324 N1325 N1326 N1327 N1328 N1329 N1330 N1331 N1332 N1333 N1334 N1335 N1336 N1337 N1338 N1339 N1340 N1341 N1342 N1343 N1344 N1345 N1346 N1347 N1348 N1349 N1350 N1351 N1352 N1353 N1354 N1355 N1356 N1357 N1358 N1359 N1360 N1361 N1362 N1363 N1364 N1365 N1366 N1367 N1368 N1369 N1370 N1371 N1372 N1373 N1374 N1375 N1376 N1377 N1378 N1379 N1380 N1381 N1382 N1383 N1384 N1385 N1386 N1387 N1388 N1389 N1390 N1391 N1392 N1393 N1394 N1395 N1396 N1397 N1398 N1399 N1400 N1401 N1402 N1403 N1404 N1405 N1406 N1407 N1408 N1409 N1410 N1411 N1412 N1413 N1414 N1415 N1416 N1417 N1418 N1419 N1420 N1421 N1422 N1423 N1424 N1425 N1426 N1427 N1428 N1429 N1430 N1431 N1432 N1433 N1434 N1435 N1436 N1437 N1438 N1439 N1440 N1441 N1442 N1443 N1444 N1445 N1446 N1447 N1448 N1449 N1450 N1451 N1452 N1453 N1454 N1455 N1456 N1457 N1458 N1459 N1460 N1461 N1462 N1463 N1464 N1465 N1466 N1467 N1468 N1469 N1470 N1471 N1472 N1473 N1474 N1475 N1476 N1477 N1478 N1479 N1480 N1481 N1482 N1483 N1484 N1485 N1486 N1487 N1488 N1489 N1490 N1491 N1492 N1493 N1494 N1495 N1496 N1497 N1498 N1499 N1500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{C54F0A28-A261-48EE-A82B-E97965671371}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{B9F1F1B0-1BD2-4893-AF9E-DA4EB0381D7D}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"M,F"</xm:f>
           </x14:formula1>

--- a/database/datas-secondaire.xlsx
+++ b/database/datas-secondaire.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t xml:space="preserve">LISTE D'ELEVES | SECONDAIRE</t>
   </si>
@@ -41,6 +41,54 @@
   </si>
   <si>
     <t>OPTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSHIKAKU TSHITOMBENU</t>
+  </si>
+  <si>
+    <t>JEAN</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17,Past. Barwani/Golf-Lido/Lubumbashi/RDC</t>
+  </si>
+  <si>
+    <t>4ème</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commerciale et Gestion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MUZALA MUKOSAYI</t>
+  </si>
+  <si>
+    <t>JACQUES</t>
+  </si>
+  <si>
+    <t>25,Rue16/Karavia/Lubumbashi/RDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mécanique Générale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KONA KEMA</t>
+  </si>
+  <si>
+    <t>LUMIERE</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>27,Rue17/Katuba/Lubumbashi/RDC</t>
+  </si>
+  <si>
+    <t>3ème</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technique des Coupes et Coutures</t>
   </si>
 </sst>
 </file>
@@ -967,60 +1015,102 @@
       <c r="S7" s="9"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="B8" s="10"/>
+      <c r="B8" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="10"/>
+      <c r="G8" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="H8" s="11"/>
-      <c r="I8" s="12"/>
+      <c r="I8" s="12">
+        <v>38641</v>
+      </c>
       <c r="J8" s="13"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="10"/>
+      <c r="K8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>11</v>
+      </c>
       <c r="M8" s="11"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="10"/>
+      <c r="N8" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="P8" s="10"/>
       <c r="Q8" s="10"/>
       <c r="R8" s="10"/>
       <c r="S8" s="10"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="B9" s="16"/>
+      <c r="B9" s="16" t="s">
+        <v>14</v>
+      </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
       <c r="F9" s="17"/>
-      <c r="G9" s="16"/>
+      <c r="G9" s="16" t="s">
+        <v>15</v>
+      </c>
       <c r="H9" s="17"/>
-      <c r="I9" s="18"/>
+      <c r="I9" s="18">
+        <v>38762</v>
+      </c>
       <c r="J9" s="19"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="16"/>
+      <c r="K9" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>16</v>
+      </c>
       <c r="M9" s="17"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="16"/>
+      <c r="N9" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="O9" s="16" t="s">
+        <v>17</v>
+      </c>
       <c r="P9" s="16"/>
       <c r="Q9" s="16"/>
       <c r="R9" s="16"/>
       <c r="S9" s="16"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="B10" s="16"/>
+      <c r="B10" s="16" t="s">
+        <v>18</v>
+      </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
       <c r="F10" s="17"/>
-      <c r="G10" s="16"/>
+      <c r="G10" s="16" t="s">
+        <v>19</v>
+      </c>
       <c r="H10" s="17"/>
-      <c r="I10" s="18"/>
+      <c r="I10" s="18">
+        <v>39523</v>
+      </c>
       <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="21"/>
+      <c r="K10" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>21</v>
+      </c>
       <c r="M10" s="22"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="16"/>
+      <c r="N10" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="O10" s="16" t="s">
+        <v>23</v>
+      </c>
       <c r="P10" s="16"/>
       <c r="Q10" s="16"/>
       <c r="R10" s="16"/>
@@ -38314,13 +38404,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{C2AB401A-2627-4389-AEE3-4A7E2F7D030F}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{96A24AC1-AD7C-4700-A1B9-F5BE8D0A838E}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"1ère,2ème,3ème,4ème,5ème,6ème,7ème E.B,8ème E.B"</xm:f>
           </x14:formula1>
           <xm:sqref>N8:N18 N19 N20 N21 N22 N23 N24 N25 N26 N27 N28 N29 N30 N31 N32 N33 N34 N35 N36 N37 N38 N39 N40 N41 N42 N43 N44 N45 N46 N47 N48 N49 N50 N51 N52 N53 N54 N55 N56 N57 N58 N59 N60 N61 N62 N63 N64 N65 N66 N67 N68 N69 N70 N71 N72 N73 N74 N75 N76 N77 N78 N79 N80 N81 N82 N83 N84 N85 N86 N87 N88 N89 N90 N91 N92 N93 N94 N95 N96 N97 N98 N99 N100 N101 N102 N103 N104 N105 N106 N107 N108 N109 N110 N111 N112 N113 N114 N115 N116 N117 N118 N119 N120 N121 N122 N123 N124 N125 N126 N127 N128 N129 N130 N131 N132 N133 N134 N135 N136 N137 N138 N139 N140 N141 N142 N143 N144 N145 N146 N147 N148 N149 N150 N151 N152 N153 N154 N155 N156 N157 N158 N159 N160 N161 N162 N163 N164 N165 N166 N167 N168 N169 N170 N171 N172 N173 N174 N175 N176 N177 N178 N179 N180 N181 N182 N183 N184 N185 N186 N187 N188 N189 N190 N191 N192 N193 N194 N195 N196 N197 N198 N199 N200 N201 N202 N203 N204 N205 N206 N207 N208 N209 N210 N211 N212 N213 N214 N215 N216 N217 N218 N219 N220 N221 N222 N223 N224 N225 N226 N227 N228 N229 N230 N231 N232 N233 N234 N235 N236 N237 N238 N239 N240 N241 N242 N243 N244 N245 N246 N247 N248 N249 N250 N251 N252 N253 N254 N255 N256 N257 N258 N259 N260 N261 N262 N263 N264 N265 N266 N267 N268 N269 N270 N271 N272 N273 N274 N275 N276 N277 N278 N279 N280 N281 N282 N283 N284 N285 N286 N287 N288 N289 N290 N291 N292 N293 N294 N295 N296 N297 N298 N299 N300 N301 N302 N303 N304 N305 N306 N307 N308 N309 N310 N311 N312 N313 N314 N315 N316 N317 N318 N319 N320 N321 N322 N323 N324 N325 N326 N327 N328 N329 N330 N331 N332 N333 N334 N335 N336 N337 N338 N339 N340 N341 N342 N343 N344 N345 N346 N347 N348 N349 N350 N351 N352 N353 N354 N355 N356 N357 N358 N359 N360 N361 N362 N363 N364 N365 N366 N367 N368 N369 N370 N371 N372 N373 N374 N375 N376 N377 N378 N379 N380 N381 N382 N383 N384 N385 N386 N387 N388 N389 N390 N391 N392 N393 N394 N395 N396 N397 N398 N399 N400 N401 N402 N403 N404 N405 N406 N407 N408 N409 N410 N411 N412 N413 N414 N415 N416 N417 N418 N419 N420 N421 N422 N423 N424 N425 N426 N427 N428 N429 N430 N431 N432 N433 N434 N435 N436 N437 N438 N439 N440 N441 N442 N443 N444 N445 N446 N447 N448 N449 N450 N451 N452 N453 N454 N455 N456 N457 N458 N459 N460 N461 N462 N463 N464 N465 N466 N467 N468 N469 N470 N471 N472 N473 N474 N475 N476 N477 N478 N479 N480 N481 N482 N483 N484 N485 N486 N487 N488 N489 N490 N491 N492 N493 N494 N495 N496 N497 N498 N499 N500 N501 N502 N503 N504 N505 N506 N507 N508 N509 N510 N511 N512 N513 N514 N515 N516 N517 N518 N519 N520 N521 N522 N523 N524 N525 N526 N527 N528 N529 N530 N531 N532 N533 N534 N535 N536 N537 N538 N539 N540 N541 N542 N543 N544 N545 N546 N547 N548 N549 N550 N551 N552 N553 N554 N555 N556 N557 N558 N559 N560 N561 N562 N563 N564 N565 N566 N567 N568 N569 N570 N571 N572 N573 N574 N575 N576 N577 N578 N579 N580 N581 N582 N583 N584 N585 N586 N587 N588 N589 N590 N591 N592 N593 N594 N595 N596 N597 N598 N599 N600 N601 N602 N603 N604 N605 N606 N607 N608 N609 N610 N611 N612 N613 N614 N615 N616 N617 N618 N619 N620 N621 N622 N623 N624 N625 N626 N627 N628 N629 N630 N631 N632 N633 N634 N635 N636 N637 N638 N639 N640 N641 N642 N643 N644 N645 N646 N647 N648 N649 N650 N651 N652 N653 N654 N655 N656 N657 N658 N659 N660 N661 N662 N663 N664 N665 N666 N667 N668 N669 N670 N671 N672 N673 N674 N675 N676 N677 N678 N679 N680 N681 N682 N683 N684 N685 N686 N687 N688 N689 N690 N691 N692 N693 N694 N695 N696 N697 N698 N699 N700 N701 N702 N703 N704 N705 N706 N707 N708 N709 N710 N711 N712 N713 N714 N715 N716 N717 N718 N719 N720 N721 N722 N723 N724 N725 N726 N727 N728 N729 N730 N731 N732 N733 N734 N735 N736 N737 N738 N739 N740 N741 N742 N743 N744 N745 N746 N747 N748 N749 N750 N751 N752 N753 N754 N755 N756 N757 N758 N759 N760 N761 N762 N763 N764 N765 N766 N767 N768 N769 N770 N771 N772 N773 N774 N775 N776 N777 N778 N779 N780 N781 N782 N783 N784 N785 N786 N787 N788 N789 N790 N791 N792 N793 N794 N795 N796 N797 N798 N799 N800 N801 N802 N803 N804 N805 N806 N807 N808 N809 N810 N811 N812 N813 N814 N815 N816 N817 N818 N819 N820 N821 N822 N823 N824 N825 N826 N827 N828 N829 N830 N831 N832 N833 N834 N835 N836 N837 N838 N839 N840 N841 N842 N843 N844 N845 N846 N847 N848 N849 N850 N851 N852 N853 N854 N855 N856 N857 N858 N859 N860 N861 N862 N863 N864 N865 N866 N867 N868 N869 N870 N871 N872 N873 N874 N875 N876 N877 N878 N879 N880 N881 N882 N883 N884 N885 N886 N887 N888 N889 N890 N891 N892 N893 N894 N895 N896 N897 N898 N899 N900 N901 N902 N903 N904 N905 N906 N907 N908 N909 N910 N911 N912 N913 N914 N915 N916 N917 N918 N919 N920 N921 N922 N923 N924 N925 N926 N927 N928 N929 N930 N931 N932 N933 N934 N935 N936 N937 N938 N939 N940 N941 N942 N943 N944 N945 N946 N947 N948 N949 N950 N951 N952 N953 N954 N955 N956 N957 N958 N959 N960 N961 N962 N963 N964 N965 N966 N967 N968 N969 N970 N971 N972 N973 N974 N975 N976 N977 N978 N979 N980 N981 N982 N983 N984 N985 N986 N987 N988 N989 N990 N991 N992 N993 N994 N995 N996 N997 N998 N999 N1000 N1001 N1002 N1003 N1004 N1005 N1006 N1007 N1008 N1009 N1010 N1011 N1012 N1013 N1014 N1015 N1016 N1017 N1018 N1019 N1020 N1021 N1022 N1023 N1024 N1025 N1026 N1027 N1028 N1029 N1030 N1031 N1032 N1033 N1034 N1035 N1036 N1037 N1038 N1039 N1040 N1041 N1042 N1043 N1044 N1045 N1046 N1047 N1048 N1049 N1050 N1051 N1052 N1053 N1054 N1055 N1056 N1057 N1058 N1059 N1060 N1061 N1062 N1063 N1064 N1065 N1066 N1067 N1068 N1069 N1070 N1071 N1072 N1073 N1074 N1075 N1076 N1077 N1078 N1079 N1080 N1081 N1082 N1083 N1084 N1085 N1086 N1087 N1088 N1089 N1090 N1091 N1092 N1093 N1094 N1095 N1096 N1097 N1098 N1099 N1100 N1101 N1102 N1103 N1104 N1105 N1106 N1107 N1108 N1109 N1110 N1111 N1112 N1113 N1114 N1115 N1116 N1117 N1118 N1119 N1120 N1121 N1122 N1123 N1124 N1125 N1126 N1127 N1128 N1129 N1130 N1131 N1132 N1133 N1134 N1135 N1136 N1137 N1138 N1139 N1140 N1141 N1142 N1143 N1144 N1145 N1146 N1147 N1148 N1149 N1150 N1151 N1152 N1153 N1154 N1155 N1156 N1157 N1158 N1159 N1160 N1161 N1162 N1163 N1164 N1165 N1166 N1167 N1168 N1169 N1170 N1171 N1172 N1173 N1174 N1175 N1176 N1177 N1178 N1179 N1180 N1181 N1182 N1183 N1184 N1185 N1186 N1187 N1188 N1189 N1190 N1191 N1192 N1193 N1194 N1195 N1196 N1197 N1198 N1199 N1200 N1201 N1202 N1203 N1204 N1205 N1206 N1207 N1208 N1209 N1210 N1211 N1212 N1213 N1214 N1215 N1216 N1217 N1218 N1219 N1220 N1221 N1222 N1223 N1224 N1225 N1226 N1227 N1228 N1229 N1230 N1231 N1232 N1233 N1234 N1235 N1236 N1237 N1238 N1239 N1240 N1241 N1242 N1243 N1244 N1245 N1246 N1247 N1248 N1249 N1250 N1251 N1252 N1253 N1254 N1255 N1256 N1257 N1258 N1259 N1260 N1261 N1262 N1263 N1264 N1265 N1266 N1267 N1268 N1269 N1270 N1271 N1272 N1273 N1274 N1275 N1276 N1277 N1278 N1279 N1280 N1281 N1282 N1283 N1284 N1285 N1286 N1287 N1288 N1289 N1290 N1291 N1292 N1293 N1294 N1295 N1296 N1297 N1298 N1299 N1300 N1301 N1302 N1303 N1304 N1305 N1306 N1307 N1308 N1309 N1310 N1311 N1312 N1313 N1314 N1315 N1316 N1317 N1318 N1319 N1320 N1321 N1322 N1323 N1324 N1325 N1326 N1327 N1328 N1329 N1330 N1331 N1332 N1333 N1334 N1335 N1336 N1337 N1338 N1339 N1340 N1341 N1342 N1343 N1344 N1345 N1346 N1347 N1348 N1349 N1350 N1351 N1352 N1353 N1354 N1355 N1356 N1357 N1358 N1359 N1360 N1361 N1362 N1363 N1364 N1365 N1366 N1367 N1368 N1369 N1370 N1371 N1372 N1373 N1374 N1375 N1376 N1377 N1378 N1379 N1380 N1381 N1382 N1383 N1384 N1385 N1386 N1387 N1388 N1389 N1390 N1391 N1392 N1393 N1394 N1395 N1396 N1397 N1398 N1399 N1400 N1401 N1402 N1403 N1404 N1405 N1406 N1407 N1408 N1409 N1410 N1411 N1412 N1413 N1414 N1415 N1416 N1417 N1418 N1419 N1420 N1421 N1422 N1423 N1424 N1425 N1426 N1427 N1428 N1429 N1430 N1431 N1432 N1433 N1434 N1435 N1436 N1437 N1438 N1439 N1440 N1441 N1442 N1443 N1444 N1445 N1446 N1447 N1448 N1449 N1450 N1451 N1452 N1453 N1454 N1455 N1456 N1457 N1458 N1459 N1460 N1461 N1462 N1463 N1464 N1465 N1466 N1467 N1468 N1469 N1470 N1471 N1472 N1473 N1474 N1475 N1476 N1477 N1478 N1479 N1480 N1481 N1482 N1483 N1484 N1485 N1486 N1487 N1488 N1489 N1490 N1491 N1492 N1493 N1494 N1495 N1496 N1497 N1498 N1499 N1500</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{B9F1F1B0-1BD2-4893-AF9E-DA4EB0381D7D}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{2F58BB8B-A892-4B47-A093-A18F9B0E7BCB}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>"M,F"</xm:f>
           </x14:formula1>
